--- a/论文写作/experiments/ablation/sources/nobatchdict以RMEO为基准十目标IGDp.xlsx
+++ b/论文写作/experiments/ablation/sources/nobatchdict以RMEO为基准十目标IGDp.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>2.2171e+2 (3.55e+1) +</t>
+          <t>2.2251e+2 (2.57e+1) +</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>1.0719e+0 (1.11e-1) =</t>
+          <t>1.0292e+0 (1.28e-1) =</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>9.0026e+2 (1.69e+2) =</t>
+          <t>9.1317e+2 (1.45e+2) =</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>9.5863e-1 (1.22e-1) +</t>
+          <t>9.8687e-1 (1.12e-1) =</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>6.2406e-1 (7.10e-2) =</t>
+          <t>6.1544e-1 (1.04e-1) =</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1.3919e+1 (1.01e+0) +</t>
+          <t>1.4110e+1 (9.65e-1) +</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9.9013e+0 (1.70e+0) +</t>
+          <t>1.1948e+1 (1.92e+0) +</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>2.9153e+0 (3.62e-2) +</t>
+          <t>2.9179e+0 (5.57e-2) +</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>2.2862e+0 (9.12e-1) =</t>
+          <t>1.7906e+0 (6.29e-1) +</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>1.6232e+0 (6.09e-2) -</t>
+          <t>1.5293e+0 (7.44e-2) =</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>5.6407e+0 (6.08e-1) +</t>
+          <t>6.0497e+0 (9.17e-1) =</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>5.2289e+0 (6.93e-1) =</t>
+          <t>5.3425e+0 (5.14e-1) =</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>3.8874e+0 (4.76e-1) +</t>
+          <t>4.1568e+0 (5.15e-1) =</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
@@ -1025,14 +1025,14 @@
       <c r="E15" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>3.9411e+0 (5.21e-1) +</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>4.1704e+0 (3.53e-1) +</t>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3.8590e+0 (4.21e-1) +</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>4.9093e+0 (2.80e-1) +</t>
+          <t>4.9547e+0 (3.01e-1) +</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>6.4647e+0 (5.03e-1) =</t>
+          <t>5.8463e+0 (5.15e-1) +</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>9/1/6</t>
+          <t>8/0/8</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
